--- a/data_hei/batch-20261008-1044/results.xlsx
+++ b/data_hei/batch-20261008-1044/results.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -845,10 +845,26 @@
           <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Piotr Różański</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Head of the Center for Engineering Studies</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>prozanski@panschelm.edu.pl</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rektorat@panschelm.edu.pl</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>82 562 06 13</t>
@@ -856,18 +872,18 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -882,7 +898,7 @@
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
@@ -948,23 +964,39 @@
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>602 188 173</t>
+        </is>
+      </c>
+      <c r="AD3" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>mgr inż. Piotr Różański ... Kierownik Centrum Studiów Inżynierskich</t>
+        </is>
+      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>no contact found</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+          <t>name, email, phone found on page</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Other role. Piotr Różański is listed as a primary contact for institutional collaboration and partnerships.</t>
+        </is>
+      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>country;contact_name;email</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -974,7 +1006,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>29 of 29 verified</t>
+          <t>35 of 35 verified</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -986,17 +1018,17 @@
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>The evidence provides a list of Erasmus+ partners, but does not state a total number of partners. Contact information for the Erasmus+ coordinator is clearly provided.</t>
+          <t>The evidence contains a partial list of Erasmus partner universities and general contact information.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>site found via: website column in the sheet. mode: gemini.</t>
+          <t>site found via: remembered from an earlier run. mode: gemini.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1127,7 +1159,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1321,7 +1353,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1390,7 +1422,11 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>postmottak@khio.no</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
@@ -1521,33 +1557,35 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" location="'Contacts'!A2"/>
+    <hyperlink ref="B2" location="'Contacts'!A2" display="Claire Collard"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
-    <hyperlink ref="M2" location="'r001 Haute Ecole Robert Schuman'!A1"/>
-    <hyperlink ref="N2" location="'r001 Haute Ecole Robert Schuman'!A1"/>
+    <hyperlink ref="M2" location="'r001 Haute Ecole Robert Schuman'!A1" display="89"/>
+    <hyperlink ref="N2" location="'r001 Haute Ecole Robert Schuman'!A1" display="3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD2" r:id="rId3"/>
+    <hyperlink ref="B3" location="'Contacts'!A3" display="Piotr Różański"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
-    <hyperlink ref="M3" location="'r002 Państwowa Akademia Nauk St'!A1"/>
-    <hyperlink ref="N3" location="'r002 Państwowa Akademia Nauk St'!A1"/>
+    <hyperlink ref="M3" location="'r002 Państwowa Akademia Nauk St'!A1" display="35"/>
+    <hyperlink ref="N3" location="'r002 Państwowa Akademia Nauk St'!A1" display="1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y3" r:id="rId6"/>
-    <hyperlink ref="B4" location="'Contacts'!A3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId7"/>
-    <hyperlink ref="M4" location="'r003 UNIVERSITAT FUR MUSIK UND'!A1"/>
-    <hyperlink ref="N4" location="'r003 UNIVERSITAT FUR MUSIK UND'!A1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="rId9"/>
-    <hyperlink ref="B5" location="'Contacts'!A5"/>
-    <hyperlink ref="I5" location="'Needs Review'!A2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId10"/>
-    <hyperlink ref="M5" location="'r004 PAEDAGOGISCHE HOCHSCHULE W'!A1"/>
-    <hyperlink ref="N5" location="'r004 PAEDAGOGISCHE HOCHSCHULE W'!A1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD5" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId14"/>
-    <hyperlink ref="N6" location="'r005 KUNSTHOGSKOLEN I OSLO KHIO'!A1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD3" r:id="rId7"/>
+    <hyperlink ref="B4" location="'Contacts'!A4" display="Lissa Gartler"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId8"/>
+    <hyperlink ref="M4" location="'r003 UNIVERSITAT FUR MUSIK UND'!A1" display="9"/>
+    <hyperlink ref="N4" location="'r003 UNIVERSITAT FUR MUSIK UND'!A1" display="2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="rId10"/>
+    <hyperlink ref="B5" location="'Contacts'!A6" display="Tim Kaiser"/>
+    <hyperlink ref="I5" location="'Needs Review'!A2" display="yes"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId11"/>
+    <hyperlink ref="M5" location="'r004 PAEDAGOGISCHE HOCHSCHULE W'!A1" display="12"/>
+    <hyperlink ref="N5" location="'r004 PAEDAGOGISCHE HOCHSCHULE W'!A1" display="1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y5" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD5" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId15"/>
+    <hyperlink ref="N6" location="'r005 KUNSTHOGSKOLEN I OSLO KHIO'!A1" display="1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1660,7 +1698,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" location="'Institutions'!A6"/>
+    <hyperlink ref="A2" location="'Institutions'!A6" display="← Back to all institutes"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1673,7 +1711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M139"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1801,7 +1839,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1868,7 +1906,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1935,7 +1973,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2002,7 +2040,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2069,7 +2107,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2136,7 +2174,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2203,7 +2241,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2270,7 +2308,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2337,7 +2375,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2404,7 +2442,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -2471,7 +2509,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2538,7 +2576,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2605,7 +2643,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2672,7 +2710,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2739,7 +2777,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2806,7 +2844,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2873,7 +2911,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2940,7 +2978,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3007,7 +3045,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3074,7 +3112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3141,7 +3179,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3208,7 +3246,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3275,7 +3313,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3342,7 +3380,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3409,7 +3447,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3476,7 +3514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3543,7 +3581,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3610,7 +3648,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3677,7 +3715,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3744,7 +3782,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3811,7 +3849,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3878,7 +3916,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3945,7 +3983,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4012,7 +4050,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4079,7 +4117,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4146,7 +4184,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4213,7 +4251,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4280,7 +4318,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4347,7 +4385,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4414,7 +4452,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4481,7 +4519,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4548,7 +4586,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4615,7 +4653,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4682,7 +4720,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4749,7 +4787,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4816,7 +4854,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4883,7 +4921,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4950,7 +4988,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5017,7 +5055,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5084,7 +5122,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5151,7 +5189,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5218,7 +5256,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5285,7 +5323,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5352,7 +5390,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5419,7 +5457,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5486,7 +5524,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5553,7 +5591,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5620,7 +5658,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5687,7 +5725,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5754,7 +5792,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5821,7 +5859,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5888,7 +5926,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5955,7 +5993,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6022,7 +6060,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6089,7 +6127,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6156,7 +6194,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6223,7 +6261,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6290,7 +6328,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6357,7 +6395,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6424,7 +6462,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6491,7 +6529,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6558,7 +6596,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6625,7 +6663,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6692,7 +6730,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6759,7 +6797,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6826,7 +6864,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6893,7 +6931,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6960,7 +6998,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7027,7 +7065,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7094,7 +7132,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7161,7 +7199,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7228,7 +7266,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7295,7 +7333,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7362,7 +7400,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7429,7 +7467,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7496,7 +7534,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7563,7 +7601,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7630,7 +7668,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7697,7 +7735,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7769,7 +7807,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7941,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -7970,7 +8008,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8075,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8142,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8209,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8276,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8343,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8410,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -8439,21 +8477,17 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Zespół Szkół nr 3 w Kraśniku</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
+          <t>Erasmus Student Network</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
           <t>International</t>
@@ -8461,7 +8495,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8491,12 +8525,12 @@
       </c>
       <c r="J102" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/wspolpraca-z-zespolem-szkol-nr-3-w-krasniku/</t>
+          <t>https://panschelm.edu.pl/erasmus/mobilnosc-studentow/</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>W dniu 28 lutego 2024 roku Państwowa Akademia Nauk Stosowanych w Chełmie reprezentowana przez JM Rektora – prof. PANS dr hab. inż. Arkadiusza Tofila podpisała porozumienie o współpracy z Zespołem Szkół nr 3 w Kraśniku reprezentowanym przez Dyrektora – mgr Annę Gromek.</t>
+          <t>W poszukiwaniu ofert można skorzystać między innymi z portalu ErasmusIntern.org, prowadzonego przez Erasmus Student Network (ESN).</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8506,14 +8540,14 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>UM w Lublinie</t>
+          <t>Akademia Górniczo-Hutnicza w Krakowie</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8558,12 +8592,12 @@
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/i-konferencja-naukowo-szkoleniowa-integracja-dla-zdrowia-efektywnosc-zespolu-interdyscyplinarnego/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Studenckie Koło Naukowe przy Katedrze Rozwoju Pielęgniarstwa UM w Lublinie</t>
+          <t>Wizyta przedstawicieli PANS w Chełmie w Akademii Górniczo-Hutniczej w Krakowie</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8573,14 +8607,14 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Akademia Górniczo-Hutnicza w Krakowie</t>
+          <t>Elektrolis</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8595,7 +8629,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8630,7 +8664,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Wizyta przedstawicieli PANS w Chełmie w Akademii Górniczo-Hutniczej w Krakowie</t>
+          <t>Firma Elektrolis – szuka pracownika</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -8640,14 +8674,14 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Elektrolis</t>
+          <t>Finder Polska</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8697,7 +8731,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Firma Elektrolis – szuka pracownika</t>
+          <t>Podpisanie listu intencyjnego z firmą Finder Polska – nowy etap współpracy</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8707,14 +8741,14 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Finder Polska</t>
+          <t>Zespół Szkół nr 3 w Kraśniku</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8729,7 +8763,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8764,7 +8798,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Podpisanie listu intencyjnego z firmą Finder Polska – nowy etap współpracy</t>
+          <t>Warsztaty Zespół Szkół nr 3 w Kraśniku</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8774,7 +8808,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8875,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8942,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +9009,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -9042,14 +9076,14 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PROSOLUTIONS</t>
+          <t>Zespołem Szkół nr 3 w Kraśniku</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9064,7 +9098,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9099,7 +9133,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Rozwijamy współpracę z PROSOLUTIONS</t>
+          <t>Współpraca z Zespołem Szkół nr 3 w Kraśniku</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9109,14 +9143,14 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Agro Antoniko Plus Sp. z o.o.</t>
+          <t>PROSOLUTIONS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9166,7 +9200,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Współpraca ze Spółką Agro Antoniko Plus Sp. z o.o.</t>
+          <t>Rozwijamy współpracę z PROSOLUTIONS</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9176,14 +9210,14 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Recykl O. O. S.A.</t>
+          <t>Spółką Agro Antoniko Plus Sp. z o.o.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9233,7 +9267,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Rozwijamy współpracę z Recykl O. O. S.A.</t>
+          <t>Współpraca ze Spółką Agro Antoniko Plus Sp. z o.o.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9243,14 +9277,14 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Gumet</t>
+          <t>Recykl O. O. S.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9300,7 +9334,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>[Gumet]</t>
+          <t>Rozwijamy współpracę z Recykl O. O. S.A.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9310,14 +9344,14 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ZS 3 w Kraśniku</t>
+          <t>Recykl Organizacja Odzysku S.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9332,7 +9366,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -9367,7 +9401,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>[ZS 3 w Kraśniku]</t>
+          <t>Wizyta studyjna: Recykl Organizacja Odzysku S.A.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9377,14 +9411,14 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Recykl Organizacja Odzysku S.A.</t>
+          <t>Gumet</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9434,7 +9468,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>[Recykl Organizacja Odzysku S.A.]</t>
+          <t>[Gumet]</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -9444,14 +9478,14 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Fabryka Łożysk Tocznych w Kraśniku</t>
+          <t>ZS 3 w Kraśniku</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9466,7 +9500,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -9501,7 +9535,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>[Fabryka Łożysk Tocznych w Kraśniku]</t>
+          <t>[ZS 3 w Kraśniku]</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -9511,14 +9545,14 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Katedra i Klinika Otorynolaryngologii, Chirurgii Głowy i Szyi Warszawskiego Uniwersytetu Medycznego</t>
+          <t>Agro Antoniko Plus Sp. z o.o.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9533,7 +9567,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -9568,7 +9602,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>[Katedra i Klinika Otorynolaryngologii, Chirurgii Głowy i Szyi Warszawskiego Uniwersytetu Medycznego]</t>
+          <t>[Agro Antoniko Plus Sp. z o.o.]</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9578,29 +9612,29 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Zagreber Philharmonie</t>
+          <t>Fabryka Łożysk Tocznych w Kraśniku</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9620,22 +9654,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J119" s="1" t="inlineStr">
         <is>
-          <t>https://www.kug.ac.at/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Festanstellung für Fran Povijač als tiefer Hornist bei der Zagreber Philharmonie</t>
+          <t>[Fabryka Łożysk Tocznych w Kraśniku]</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9645,29 +9679,29 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:28Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Tonhalle Orchester Zürich</t>
+          <t>Katedra i Klinika Otorynolaryngologii, Chirurgii Głowy i Szyi Warszawskiego Uniwersytetu Medycznego</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -9687,22 +9721,22 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J120" s="1" t="inlineStr">
         <is>
-          <t>https://www.kug.ac.at/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Engagement beim Tonhalle Orchester Zürich für Hornist Daniel Dubrovsky.</t>
+          <t>[Katedra i Klinika Otorynolaryngologii, Chirurgii Głowy i Szyi Warszawskiego Uniwersytetu Medycznego]</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9712,34 +9746,34 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:28Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Hochschule</t>
+          <t>Muzeum Ziemi Chełmskiej im. Wiktora Ambroziewicza w Chełmie</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9754,22 +9788,22 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J121" s="1" t="inlineStr">
         <is>
-          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Staff Mobility for Training (STT) ermöglicht Mitarbeitenden der KUG einen Fort- oder Weiterbildungsaufenthalt an einer Hochschule, in einem Unternehmen oder in einer anderen geeigneten Organisation im Ausland. Ziele sind die berufliche Weiterbildung, der internationale Austausch und die Vernetzung mit Fachkolleg*innen.</t>
+          <t>[Muzeum Ziemi Chełmskiej im. Wiktora Ambroziewicza w Chełmie]</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9779,24 +9813,24 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:28Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Unternehmen</t>
+          <t>Centrum Medyczne Aurismed</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -9806,7 +9840,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9821,22 +9855,22 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J122" s="1" t="inlineStr">
         <is>
-          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Staff Mobility for Training (STT) ermöglicht Mitarbeitenden der KUG einen Fort- oder Weiterbildungsaufenthalt an einer Hochschule, in einem Unternehmen oder in einer anderen geeigneten Organisation im Ausland. Ziele sind die berufliche Weiterbildung, der internationale Austausch und die Vernetzung mit Fachkolleg*innen.</t>
+          <t>[Centrum Medyczne Aurismed]</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9846,24 +9880,24 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:28Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>andere geeignete Organisation</t>
+          <t>Muzeum Regionalne w Krasnymstawie</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -9873,7 +9907,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -9888,22 +9922,22 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J123" s="1" t="inlineStr">
         <is>
-          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Staff Mobility for Training (STT) ermöglicht Mitarbeitenden der KUG einen Fort- oder Weiterbildungsaufenthalt an einer Hochschule, in einem Unternehmen oder in einer anderen geeigneten Organisation im Ausland. Ziele sind die berufliche Weiterbildung, der internationale Austausch und die Vernetzung mit Fachkolleg*innen.</t>
+          <t>[Muzeum Regionalne w Krasnymstawie]</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9913,34 +9947,34 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:28Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Partnerhochschule</t>
+          <t>Haber</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9955,22 +9989,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J124" s="1" t="inlineStr">
         <is>
-          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Staff Mobility for Teaching Assignment (STA) richtet sich an Lehrende bzw. Personen, die von einer Partnerhochschule eingeladen wurden, dort zu unterrichten. Der Lehraufenthalt soll in das Studienprogramm der Partnerhochschule eingebunden sein und einen erkennbaren Mehrwert für deren Studierende und Lehrende bieten.</t>
+          <t>[Haber]</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9980,29 +10014,29 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:28Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Sigma</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -10022,22 +10056,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J125" s="1" t="inlineStr">
         <is>
-          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Einladung oder Annahmebestätigung: Sie benötigen eine schriftliche Zusage der aufnehmenden Hochschule, Organisation oder des Unternehmens.</t>
+          <t>[Sigma]</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -10047,14 +10081,14 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:28Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Gasthochschule</t>
+          <t>Zagreber Philharmonie</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10069,12 +10103,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -10099,17 +10133,17 @@
       </c>
       <c r="J126" s="1" t="inlineStr">
         <is>
-          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
+          <t>https://www.kug.ac.at/</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Der Lehraufenthalt muss einen wesentlichen Beitrag zum Studienprogramm der Gasthochschule leisten und in dieses integriert sein.</t>
+          <t>Festanstellung für Fran Povijač als tiefer Hornist bei der Zagreber Philharmonie</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10121,7 +10155,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Europäische Kommission</t>
+          <t>Tonhalle Orchester Zürich</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10166,17 +10200,17 @@
       </c>
       <c r="J127" s="1" t="inlineStr">
         <is>
-          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
+          <t>https://www.kug.ac.at/</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Füllen Sie innerhalb von 30 Kalendertagen nach Ende der Mobilität den verpflichtenden Online-Abschlussbericht der Europäischen Kommission (EU-Survey) aus. Den Link erhalten Sie automatisch per E-Mail.</t>
+          <t>Engagement beim Tonhalle Orchester Zürich für Hornist Daniel Dubrovsky.</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10188,17 +10222,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Florida International University</t>
+          <t>Hochschule</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10208,7 +10242,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -10223,59 +10257,59 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r003</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
         </is>
       </c>
       <c r="J128" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de</t>
+          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Internationale Forschungskooperationen sind ein wichtiger Bestandteil meiner wissenschaftlichen Arbeit an der PH Weingarten. Im Rahmen des Fulbright Visiting Scholar Program 2026/27 werde ich einen Forschungsaufenthalt an der Florida International University absolvieren und dort zu antialevitischer und antisemitischer Propaganda sowie transnationalen Einflussstrategien forschen. Zugleich bin ich für zwei Jahre Faculty Fellow am Møller Institute, Churchill College, University of Cambridge, wo ich</t>
+          <t>Staff Mobility for Training (STT) ermöglicht Mitarbeitenden der KUG einen Fort- oder Weiterbildungsaufenthalt an einer Hochschule, in einem Unternehmen oder in einer anderen geeigneten Organisation im Ausland. Ziele sind die berufliche Weiterbildung, der internationale Austausch und die Vernetzung mit Fachkolleg*innen.</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-10-08T18:29:06Z</t>
+          <t>2026-10-08T18:28:28Z</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>University of Cambridge</t>
+          <t>Unternehmen</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -10290,59 +10324,59 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r003</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
         </is>
       </c>
       <c r="J129" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de</t>
+          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Internationale Forschungskooperationen sind ein wichtiger Bestandteil meiner wissenschaftlichen Arbeit an der PH Weingarten. Im Rahmen des Fulbright Visiting Scholar Program 2026/27 werde ich einen Forschungsaufenthalt an der Florida International University absolvieren und dort zu antialevitischer und antisemitischer Propaganda sowie transnationalen Einflussstrategien forschen. Zugleich bin ich für zwei Jahre Faculty Fellow am Møller Institute, Churchill College, University of Cambridge, wo ich</t>
+          <t>Staff Mobility for Training (STT) ermöglicht Mitarbeitenden der KUG einen Fort- oder Weiterbildungsaufenthalt an einer Hochschule, in einem Unternehmen oder in einer anderen geeigneten Organisation im Ausland. Ziele sind die berufliche Weiterbildung, der internationale Austausch und die Vernetzung mit Fachkolleg*innen.</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-10-08T18:29:06Z</t>
+          <t>2026-10-08T18:28:28Z</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Wissenschaftsverbund Vierländerregion Bodensee</t>
+          <t>andere geeignete Organisation</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Germany/Switzerland/Austria</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -10357,49 +10391,49 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r003</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
         </is>
       </c>
       <c r="J130" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/studium/studierendenservice/auslandsaufenthalt/modulmobilitaet</t>
+          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Seit Beginn des Wintersemesters 2023/24 haben Studierende der PH Weingarten innerhalb des Wissenschaftsverbundes Vierländerregion Bodensee die Möglichkeit landesübergreifend einzelne Lehrveranstaltungen bzw. Module an Mitgliedshochschulen des Wissenschaftsverbundes zu besuchen. Dabei profitieren sie von einer enormen Vielfalt von Fächern, Fachbereichen und spezifischen Lehrveranstaltungen. Einer begrenzten Anzahl von Teilnehmenden kann im Rahmen der Modulmobiltät eine finanzielle Unterstützung a</t>
+          <t>Staff Mobility for Training (STT) ermöglicht Mitarbeitenden der KUG einen Fort- oder Weiterbildungsaufenthalt an einer Hochschule, in einem Unternehmen oder in einer anderen geeigneten Organisation im Ausland. Ziele sind die berufliche Weiterbildung, der internationale Austausch und die Vernetzung mit Fachkolleg*innen.</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-10-08T18:29:06Z</t>
+          <t>2026-10-08T18:28:28Z</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Universität Konstanz</t>
+          <t>Partnerhochschule</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10409,7 +10443,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -10424,54 +10458,54 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r003</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
         </is>
       </c>
       <c r="J131" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/studium/studierendenservice/auslandsaufenthalt/modulmobilitaet</t>
+          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Informationen zu den teilnehmenden Hochschulen, deren Studienangebot sowie zum Bewerbungsverfahren finden Sie auf der Webseite der Koordinationsstelle an der Universität Konstanz.</t>
+          <t>Staff Mobility for Teaching Assignment (STA) richtet sich an Lehrende bzw. Personen, die von einer Partnerhochschule eingeladen wurden, dort zu unterrichten. Der Lehraufenthalt soll in das Studienprogramm der Partnerhochschule eingebunden sein und einen erkennbaren Mehrwert für deren Studierende und Lehrende bieten.</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-10-08T18:29:06Z</t>
+          <t>2026-10-08T18:28:28Z</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Universität Graz</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -10491,49 +10525,49 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r003</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
         </is>
       </c>
       <c r="J132" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+          <t>Einladung oder Annahmebestätigung: Sie benötigen eine schriftliche Zusage der aufnehmenden Hochschule, Organisation oder des Unternehmens.</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-10-08T18:29:06Z</t>
+          <t>2026-10-08T18:28:28Z</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Universität Minho</t>
+          <t>Gasthochschule</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -10543,7 +10577,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -10558,54 +10592,54 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r003</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
         </is>
       </c>
       <c r="J133" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+          <t>Der Lehraufenthalt muss einen wesentlichen Beitrag zum Studienprogramm der Gasthochschule leisten und in dieses integriert sein.</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-10-08T18:29:06Z</t>
+          <t>2026-10-08T18:28:28Z</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Universität Växjö</t>
+          <t>Europäische Kommission</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Country not stated</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -10625,44 +10659,44 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r003</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
         </is>
       </c>
       <c r="J134" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+          <t>https://international.kug.ac.at/personalmobilitaet/outgoing-personal/erasmus-personalmobilitaet</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+          <t>Füllen Sie innerhalb von 30 Kalendertagen nach Ende der Mobilität den verpflichtenden Online-Abschlussbericht der Europäischen Kommission (EU-Survey) aus. Den Link erhalten Sie automatisch per E-Mail.</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-10-08T18:29:06Z</t>
+          <t>2026-10-08T18:28:28Z</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Møller Institute, Churchill College, University of Cambridge</t>
+          <t>Florida International University</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10712,7 +10746,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10724,12 +10758,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Landkreis Ravensburg</t>
+          <t>University of Cambridge</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -10739,7 +10773,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -10774,12 +10808,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Das Kunstcamp der Pädagogischen Hochschule Weingarten (PH) und des Landkreises Ravensburg auf Schloss Achberg fand auch in diesem Jahr wieder großes Interesse: 37 Jugendliche im Alter von 14 bis 21 Jahren haben an kreativen Workshops teilgenommen und verschiedene Kunstformen kennengelernt.</t>
+          <t>Internationale Forschungskooperationen sind ein wichtiger Bestandteil meiner wissenschaftlichen Arbeit an der PH Weingarten. Im Rahmen des Fulbright Visiting Scholar Program 2026/27 werde ich einen Forschungsaufenthalt an der Florida International University absolvieren und dort zu antialevitischer und antisemitischer Propaganda sowie transnationalen Einflussstrategien forschen. Zugleich bin ich für zwei Jahre Faculty Fellow am Møller Institute, Churchill College, University of Cambridge, wo ich</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -10791,12 +10825,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Universidade Federal de Santa Catarina</t>
+          <t>Wissenschaftsverbund Vierländerregion Bodensee</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Brasilien</t>
+          <t>Germany/Switzerland/Austria</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -10806,12 +10840,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>study</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -10836,17 +10870,17 @@
       </c>
       <c r="J137" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+          <t>https://www.ph-weingarten.de/de/studium/studierendenservice/auslandsaufenthalt/modulmobilitaet</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Donnerstag, 22.10.26 Präsentation von Dr. Elaine Roschel, Universidade Federal de Santa Catarina, Brasilien</t>
+          <t>Seit Beginn des Wintersemesters 2023/24 haben Studierende der PH Weingarten innerhalb des Wissenschaftsverbundes Vierländerregion Bodensee die Möglichkeit landesübergreifend einzelne Lehrveranstaltungen bzw. Module an Mitgliedshochschulen des Wissenschaftsverbundes zu besuchen. Dabei profitieren sie von einer enormen Vielfalt von Fächern, Fachbereichen und spezifischen Lehrveranstaltungen. Einer begrenzten Anzahl von Teilnehmenden kann im Rahmen der Modulmobiltät eine finanzielle Unterstützung a</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -10858,17 +10892,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Kooperationshochschulen in Europa</t>
+          <t>Universität Konstanz</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10903,17 +10937,17 @@
       </c>
       <c r="J138" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/studium/bachelorstudiengaenge/medien-und-bildungsmanagement</t>
+          <t>https://www.ph-weingarten.de/de/studium/studierendenservice/auslandsaufenthalt/modulmobilitaet</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Die Pädagogische Hochschule Weingarten und der Studiengang Medien- und Bildungsmanagement bieten auch für Auslandssemester Möglichkeiten an. Neben Kooperationshochschulen in ganz Europa, bestehen auch Kooperation mit Hochschule in Übersee (z. B. in Brasilien, Argentinien, USA oder Japan). Studierende des Medien- und Bildungsmanagements haben bisher Auslandserfahrungen in Schweden, Italien, Polen, Südkorea aber auch den USA und Südafrika gesammelt. Immer wieder besuchen Studierende von Partnerhoc</t>
+          <t>Informationen zu den teilnehmenden Hochschulen, deren Studienangebot sowie zum Bewerbungsverfahren finden Sie auf der Webseite der Koordinationsstelle an der Universität Konstanz.</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -10925,65 +10959,534 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>Universität Graz</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J139" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:29:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Universität Minho</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J140" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:29:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Universität Växjö</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J141" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:29:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Møller Institute, Churchill College, University of Cambridge</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J142" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Internationale Forschungskooperationen sind ein wichtiger Bestandteil meiner wissenschaftlichen Arbeit an der PH Weingarten. Im Rahmen des Fulbright Visiting Scholar Program 2026/27 werde ich einen Forschungsaufenthalt an der Florida International University absolvieren und dort zu antialevitischer und antisemitischer Propaganda sowie transnationalen Einflussstrategien forschen. Zugleich bin ich für zwei Jahre Faculty Fellow am Møller Institute, Churchill College, University of Cambridge, wo ich</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:29:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Landkreis Ravensburg</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J143" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Das Kunstcamp der Pädagogischen Hochschule Weingarten (PH) und des Landkreises Ravensburg auf Schloss Achberg fand auch in diesem Jahr wieder großes Interesse: 37 Jugendliche im Alter von 14 bis 21 Jahren haben an kreativen Workshops teilgenommen und verschiedene Kunstformen kennengelernt.</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:29:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Santa Catarina</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J144" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Donnerstag, 22.10.26 Präsentation von Dr. Elaine Roschel, Universidade Federal de Santa Catarina, Brasilien</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:29:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Kooperationshochschulen in Europa</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J145" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/studium/bachelorstudiengaenge/medien-und-bildungsmanagement</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Die Pädagogische Hochschule Weingarten und der Studiengang Medien- und Bildungsmanagement bieten auch für Auslandssemester Möglichkeiten an. Neben Kooperationshochschulen in ganz Europa, bestehen auch Kooperation mit Hochschule in Übersee (z. B. in Brasilien, Argentinien, USA oder Japan). Studierende des Medien- und Bildungsmanagements haben bisher Auslandserfahrungen in Schweden, Italien, Polen, Südkorea aber auch den USA und Südafrika gesammelt. Immer wieder besuchen Studierende von Partnerhoc</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:29:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>Hochschule in Übersee</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>study</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
         <is>
           <t>r004</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I146" t="inlineStr">
         <is>
           <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
         </is>
       </c>
-      <c r="J139" s="1" t="inlineStr">
+      <c r="J146" s="1" t="inlineStr">
         <is>
           <t>https://www.ph-weingarten.de/de/studium/bachelorstudiengaenge/medien-und-bildungsmanagement</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="K146" t="inlineStr">
         <is>
           <t>Die Pädagogische Hochschule Weingarten und der Studiengang Medien- und Bildungsmanagement bieten auch für Auslandssemester Möglichkeiten an. Neben Kooperationshochschulen in ganz Europa, bestehen auch Kooperation mit Hochschule in Übersee (z. B. in Brasilien, Argentinien, USA oder Japan). Studierende des Medien- und Bildungsmanagements haben bisher Auslandserfahrungen in Schweden, Italien, Polen, Südkorea aber auch den USA und Südafrika gesammelt. Immer wieder besuchen Studierende von Partnerhoc</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr">
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t>2026-10-08T18:29:06Z</t>
         </is>
@@ -11129,6 +11632,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId145"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11248,7 +11758,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -11305,7 +11815,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -11362,7 +11872,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -11389,7 +11899,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Polska</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11424,7 +11934,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:30Z</t>
+          <t>2026-10-22T11:32:59Z</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11986,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -11533,7 +12043,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -11590,7 +12100,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -11677,7 +12187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11802,19 +12312,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11824,34 +12334,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lissa Gartler</t>
+          <t>Piotr Różański</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Office of the Vice Rector for Teaching &amp; International Affairs</t>
+          <t>Head of the Center for Engineering Studies</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lissa.gartler@kug.ac.at</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>prozanski@panschelm.edu.pl</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>602 188 173</t>
+        </is>
+      </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://www.kug.ac.at/kunst/gesellschaft/nachhaltigkeit/klimaneutraler-universitaetsbetrieb/betriebliches-mobilitaetsmanagement</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kontakt: Mag.a Lissa Gartler, Büro der Vizerektorin für Lehre &amp; Internationales, lissa.gartler(at)kug.ac.at</t>
+          <t>mgr inż. Piotr Różański ... Kierownik Centrum Studiów Inżynierskich</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Head of international relations. Lissa Gartler is the contact person for mobility and international affairs within the office of the Vice Rector for Teaching and International Affairs. Own work email found on a page naming them.</t>
+          <t>Other role. Piotr Różański is listed as a primary contact for institutional collaboration and partnerships.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -11861,7 +12375,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>name, email, phone found on page</t>
         </is>
       </c>
     </row>
@@ -11878,35 +12392,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Anika Stiawa</t>
+          <t>Lissa Gartler</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Outgoing Student Mobility Coordinator</t>
+          <t>Office of the Vice Rector for Teaching &amp; International Affairs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>lissa.gartler@kug.ac.at</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>https://international.kug.ac.at/studierendenmobilitaet/outgoing-studierende/erasmus-kurzzeit</t>
+          <t>https://www.kug.ac.at/kunst/gesellschaft/nachhaltigkeit/klimaneutraler-universitaetsbetrieb/betriebliches-mobilitaetsmanagement</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Anika Stiawa ... outgoing_students(at)kug.ac.at</t>
+          <t>Kontakt: Mag.a Lissa Gartler, Büro der Vizerektorin für Lehre &amp; Internationales, lissa.gartler(at)kug.ac.at</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Mobility coordinator. Anika Stiawa is the contact person for outgoing student mobility at the International Office.</t>
+          <t>Head of international relations. Lissa Gartler is the contact person for mobility and international affairs within the office of the Vice Rector for Teaching and International Affairs. Own work email found on a page naming them.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -11916,66 +12434,62 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>name found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tim Kaiser</t>
+          <t>Anika Stiawa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Head of International Office</t>
+          <t>Outgoing Student Mobility Coordinator</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0751/ 501-8421</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/studium/studierendenservice/auslandsaufenthalt/modulmobilitaet</t>
+          <t>https://international.kug.ac.at/studierendenmobilitaet/outgoing-studierende/erasmus-kurzzeit</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kaiser, Dr. Tim ... Leitung</t>
+          <t>Anika Stiawa ... outgoing_students(at)kug.ac.at</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Matches the contact your operators already spoke to. Head of international relations. Tim Kaiser is the Head of the International Office and the contact person for mobility programs.</t>
+          <t>Mobility coordinator. Anika Stiawa is the contact person for outgoing student mobility at the International Office.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -11992,39 +12506,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kim Enderle</t>
+          <t>Tim Kaiser</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>International Coordinator Erasmus / Auslandspraktika</t>
+          <t>Head of International Office</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0751/ 501-8049</t>
+          <t>0751/ 501-8421</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+          <t>https://www.ph-weingarten.de/de/studium/studierendenservice/auslandsaufenthalt/modulmobilitaet</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>International Coordinator Erasmus / Auslandspraktika ... Enderle, Kim</t>
+          <t>Kaiser, Dr. Tim ... Leitung</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Institutional Erasmus+ coordinator. Kim Enderle is the designated International Coordinator for Erasmus and internships.</t>
+          <t>Matches the contact your operators already spoke to. Head of international relations. Tim Kaiser is the Head of the International Office and the contact person for mobility programs.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -12034,7 +12548,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
@@ -12051,49 +12565,108 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Beate Irion</t>
+          <t>Kim Enderle</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>International Coordinator Overseas</t>
+          <t>International Coordinator Erasmus / Auslandspraktika</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
+          <t>0751/ 501-8049</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>International Coordinator Erasmus / Auslandspraktika ... Enderle, Kim</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Institutional Erasmus+ coordinator. Kim Enderle is the designated International Coordinator for Erasmus and internships.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>cited page was not read by the fetcher (cannot check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Beate Irion</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>International Coordinator Overseas</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>0751/ 501-8050</t>
         </is>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>International Coordinator Übersee ... Irion, Beate</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>International relations officer. Beate Irion serves as the International Coordinator for overseas partnerships.</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>name not on page</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
@@ -12105,6 +12678,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12189,7 +12763,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12800,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12837,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
@@ -15787,7 +16361,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" location="'Institutions'!A2"/>
+    <hyperlink ref="A2" location="'Institutions'!A2" display="← Back to all institutes"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
@@ -15891,7 +16465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -15920,7 +16494,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>International partners (28) - those with no country stated are last</t>
+          <t>International partners (35) - those with no country stated are last</t>
         </is>
       </c>
     </row>
@@ -16371,14 +16945,10 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zespół Szkół nr 3 w Kraśniku</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
+          <t>Erasmus Student Network</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>International</t>
@@ -16386,7 +16956,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16401,14 +16971,14 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/wspolpraca-z-zespolem-szkol-nr-3-w-krasniku/</t>
+          <t>https://panschelm.edu.pl/erasmus/mobilnosc-studentow/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UM w Lublinie</t>
+          <t>Akademia Górniczo-Hutnicza w Krakowie</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -16438,14 +17008,14 @@
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/i-konferencja-naukowo-szkoleniowa-integracja-dla-zdrowia-efektywnosc-zespolu-interdyscyplinarnego/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Akademia Górniczo-Hutnicza w Krakowie</t>
+          <t>Elektrolis</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -16460,7 +17030,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16482,7 +17052,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Elektrolis</t>
+          <t>Finder Polska</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -16519,7 +17089,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Finder Polska</t>
+          <t>Zespół Szkół nr 3 w Kraśniku</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -16534,7 +17104,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -16704,7 +17274,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PROSOLUTIONS</t>
+          <t>Zespołem Szkół nr 3 w Kraśniku</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -16719,7 +17289,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -16741,7 +17311,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Agro Antoniko Plus Sp. z o.o.</t>
+          <t>PROSOLUTIONS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -16778,7 +17348,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Recykl O. O. S.A.</t>
+          <t>Spółką Agro Antoniko Plus Sp. z o.o.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -16815,7 +17385,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gumet</t>
+          <t>Recykl O. O. S.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -16852,7 +17422,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ZS 3 w Kraśniku</t>
+          <t>Recykl Organizacja Odzysku S.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -16867,7 +17437,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -16889,7 +17459,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Recykl Organizacja Odzysku S.A.</t>
+          <t>Gumet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -16926,7 +17496,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fabryka Łożysk Tocznych w Kraśniku</t>
+          <t>ZS 3 w Kraśniku</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -16941,7 +17511,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -16963,108 +17533,367 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Agro Antoniko Plus Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Fabryka Łożysk Tocznych w Kraśniku</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Katedra i Klinika Otorynolaryngologii, Chirurgii Głowy i Szyi Warszawskiego Uniwersytetu Medycznego</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Campuses (1)</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Campus</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Verified?</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Muzeum Ziemi Chełmskiej im. Wiktora Ambroziewicza w Chełmie</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Centrum Medyczne Aurismed</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Muzeum Regionalne w Krasnymstawie</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Haber</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sigma</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Campuses (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Campus</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Verified?</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Polska</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Chełm</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>https://panschelm.edu.pl/</t>
         </is>
@@ -17072,7 +17901,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" location="'Institutions'!A3"/>
+    <hyperlink ref="A2" location="'Institutions'!A3" display="← Back to all institutes"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
@@ -17101,7 +17930,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17624,7 +18460,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" location="'Institutions'!A4"/>
+    <hyperlink ref="A2" location="'Institutions'!A4" display="← Back to all institutes"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
@@ -18236,7 +19072,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" location="'Institutions'!A5"/>
+    <hyperlink ref="A2" location="'Institutions'!A5" display="← Back to all institutes"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>

--- a/data_hei/batch-20261008-1044/results.xlsx
+++ b/data_hei/batch-20261008-1044/results.xlsx
@@ -981,7 +981,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>name, email, phone found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1419,21 +1419,33 @@
           <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Anna Elisabet Einarsson</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Project manager</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>postmottak@khio.no</t>
+          <t>exchange@khio.no</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1441,7 +1453,7 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/</t>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1449,10 +1461,14 @@
           <t>university</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr">
@@ -1496,25 +1512,49 @@
           <t>ketiaker@khio.no</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AD6" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Project manager | ... Anna Elisabet Einarsson</t>
+        </is>
+      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>no contact found</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+          <t>name found on page</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Other role. Anna Elisabet Einarsson is the project manager for the international cooperation project Opera Out of Opera 2.</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>contact_name</t>
+        </is>
+      </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1524,29 +1564,33 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>none published</t>
+          <t>21 verified of ~100 stated (rest of the list not readable)</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1 of 1 verified</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr"/>
+          <t>1 verified of ~100 stated (rest of the list not readable)</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>The provided evidence does not contain any information regarding international mobility coordinators, Erasmus+ partners, or specific contact persons for international relations.</t>
+          <t>The evidence provides a list of specific project partners and networks, but does not contain a comprehensive list of all bilateral partner institutions.</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>site found via: website column in the sheet. mode: gemini.</t>
+          <t>site found via: remembered from an earlier run. mode: gemini (read by the paid reader gemini-3.1-flash-lite (paid key): free Gemini was unavailable).</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:39Z</t>
+          <t>2026-10-22T13:17:47Z</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1584,8 +1628,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y5" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD5" r:id="rId14"/>
+    <hyperlink ref="B6" location="'Contacts'!A9" display="Anna Elisabet Einarsson"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId15"/>
+    <hyperlink ref="M6" location="'r005 KUNSTHOGSKOLEN I OSLO KHIO'!A1" display="16"/>
     <hyperlink ref="N6" location="'r005 KUNSTHOGSKOLEN I OSLO KHIO'!A1" display="1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD6" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1597,7 +1645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1626,14 +1674,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Campuses (1)</t>
+          <t>International partners (16) - those with no country stated are last</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Campus</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1643,15 +1691,19 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>International or National?</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Mobility</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Verified?</t>
@@ -1666,33 +1718,665 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Mozarteum University Salzburg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Stockholm University of the Arts – SKH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Escola Superior de Música e Artes do Espetáculo do Porto</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nova Opera</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WallMuse</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jeunesses Musicales Croatia HGM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AEC – Association Européenne des Conservatoires</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ELIA (The European League of Institutes of the Arts)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KUNO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nordic-Baltic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CIRRUS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nordic-Baltic</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CUMULUS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ecoles des écoles</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NordOpera</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>The Society of Artistic Research (SAR)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Conservatorio di Musica Santa Cecilia</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Norteas</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/intranet/for-staff/internationalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Campuses (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Campus</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Verified?</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Kunsthøgskolen i Oslo</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Oslo</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>https://khio.no/om-kunsthogskolen-i-oslo/kontaktinfo</t>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/om-kunsthogskolen-i-oslo/kontaktinfo#kart-over-campus</t>
         </is>
       </c>
     </row>
@@ -1700,6 +2384,22 @@
   <hyperlinks>
     <hyperlink ref="A2" location="'Institutions'!A6" display="← Back to all institutes"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1711,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M146"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7802,7 +8502,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7869,7 +8569,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7936,7 +8636,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -8003,7 +8703,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -8070,7 +8770,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8137,7 +8837,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8204,7 +8904,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8271,7 +8971,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8338,7 +9038,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8405,7 +9105,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8472,7 +9172,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8535,7 +9235,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8602,7 +9302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8669,7 +9369,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8736,7 +9436,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8803,7 +9503,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8870,7 +9570,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8937,7 +9637,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -9004,7 +9704,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -9071,7 +9771,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -9138,7 +9838,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -9205,7 +9905,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9272,7 +9972,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9339,7 +10039,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9406,7 +10106,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9473,7 +10173,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9540,7 +10240,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9607,7 +10307,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -9674,7 +10374,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -9741,7 +10441,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -9808,7 +10508,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9875,7 +10575,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9942,7 +10642,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -10009,7 +10709,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -10076,7 +10776,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -11489,6 +12189,1078 @@
       <c r="M146" t="inlineStr">
         <is>
           <t>2026-10-08T18:29:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Mozarteum University Salzburg</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J147" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Mozarteum University Salzburg (Austria)</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Stockholm University of the Arts – SKH</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J148" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Stockholm University of the Arts – SKH (Sweden)</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Escola Superior de Música e Artes do Espetáculo do Porto</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J149" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Escola Superior de Música e Artes do Espetáculo do Porto (Portugal)</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Nova Opera</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J150" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Nova Opera (Ukraine)</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>WallMuse</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J151" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>WallMuse (France)</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Jeunesses Musicales Croatia HGM</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J152" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Jeunesses Musicales Croatia HGM (Croatia)</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>AEC – Association Européenne des Conservatoires</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J153" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>AEC – Association Européenne des Conservatoires (Belgium)</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ELIA (The European League of Institutes of the Arts)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J154" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>ELIA (The European League of Institutes of the Arts)</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>KUNO</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Nordic-Baltic</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J155" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>KUNO - An Art Academy Without Walls</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CIRRUS</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Nordic-Baltic</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J156" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>CIRRUS - Nordic Baltic Net of Art and Design Education</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CUMULUS</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J157" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>CUMULUS - International Association of Universities and Colleges of Art, Design and Media</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Ecoles des écoles</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J158" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Ecoles des écoles</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>NordOpera</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J159" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>NordOpera (Opera)</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>The Society of Artistic Research (SAR)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J160" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts#networks-and-cooperation</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>The Society of Artistic Research (SAR)</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Conservatorio di Musica Santa Cecilia</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J161" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>The project is coordinated by Conservatorio di Musica Santa Cecilia (Rome) and the following project partners:</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Norteas</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J162" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/intranet/for-staff/internationalization</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Norteas (Performing Arts)</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:17:47Z</t>
         </is>
       </c>
     </row>
@@ -11639,6 +13411,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11929,7 +13717,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -12142,12 +13930,12 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/om-kunsthogskolen-i-oslo/kontaktinfo</t>
+          <t>https://khio.no/om-kunsthogskolen-i-oslo/kontaktinfo#kart-over-campus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kunsthøgskolen i Oslo held til i Fossveien 24 på Grünerløkka, i den ombygde Seilduksfabrikken, rett ved Akerselva. Med eit areal på 43 000 m2 er dette eit av Nord-Europas største anlegg for kunst og design.</t>
+          <t>Fossveien 24, Grünerløkka</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -12162,7 +13950,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-08T18:28:39Z</t>
+          <t>2026-10-22T13:17:47Z</t>
         </is>
       </c>
     </row>
@@ -12187,7 +13975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12375,7 +14163,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>name, email, phone found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -12667,6 +14455,61 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>cited page was not read by the fetcher (cannot check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Anna Elisabet Einarsson</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Project manager</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Project manager | ... Anna Elisabet Einarsson</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Other role. Anna Elisabet Einarsson is the project manager for the international cooperation project Opera Out of Opera 2.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>name found on page</t>
         </is>
       </c>
     </row>
@@ -12679,6 +14522,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
